--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/181.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/181.xlsx
@@ -426,13 +426,13 @@
         <v>-3.742325010234358</v>
       </c>
       <c r="E2">
-        <v>-15.41701069686103</v>
+        <v>-14.85620447575113</v>
       </c>
       <c r="F2">
-        <v>2.107410685498339</v>
+        <v>1.783476310142523</v>
       </c>
       <c r="G2">
-        <v>-14.47961557214956</v>
+        <v>-16.19650090481653</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-3.422289212513523</v>
       </c>
       <c r="E3">
-        <v>-15.89195252231149</v>
+        <v>-15.00283193564549</v>
       </c>
       <c r="F3">
-        <v>2.227262381766965</v>
+        <v>1.95261135079371</v>
       </c>
       <c r="G3">
-        <v>-15.00360044374156</v>
+        <v>-14.90833121948518</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-2.986787509229131</v>
       </c>
       <c r="E4">
-        <v>-15.63452236039745</v>
+        <v>-14.52861013756225</v>
       </c>
       <c r="F4">
-        <v>1.998011448271612</v>
+        <v>1.896025538435058</v>
       </c>
       <c r="G4">
-        <v>-13.89422670189517</v>
+        <v>-15.35982838594929</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-2.500932256154268</v>
       </c>
       <c r="E5">
-        <v>-15.59589900558603</v>
+        <v>-16.75190973636809</v>
       </c>
       <c r="F5">
-        <v>2.272824017248242</v>
+        <v>2.325111651752391</v>
       </c>
       <c r="G5">
-        <v>-13.93688804698698</v>
+        <v>-14.49154843354587</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-1.981991128880709</v>
       </c>
       <c r="E6">
-        <v>-17.33414469648228</v>
+        <v>-16.6563951625983</v>
       </c>
       <c r="F6">
-        <v>2.360814717910058</v>
+        <v>2.146827542027711</v>
       </c>
       <c r="G6">
-        <v>-12.81306046331613</v>
+        <v>-14.28310489948396</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-1.468818465071712</v>
       </c>
       <c r="E7">
-        <v>-17.17093396477183</v>
+        <v>-16.36828006080829</v>
       </c>
       <c r="F7">
-        <v>2.404501245587455</v>
+        <v>2.290354058026242</v>
       </c>
       <c r="G7">
-        <v>-12.35576818688553</v>
+        <v>-13.98592053696913</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-0.9917026413478289</v>
       </c>
       <c r="E8">
-        <v>-17.25983243801641</v>
+        <v>-18.90347377841842</v>
       </c>
       <c r="F8">
-        <v>2.651028826914337</v>
+        <v>2.31888927121063</v>
       </c>
       <c r="G8">
-        <v>-12.22868958581506</v>
+        <v>-11.75275893799836</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-0.5797341084986333</v>
       </c>
       <c r="E9">
-        <v>-18.4605527926762</v>
+        <v>-19.45101157068584</v>
       </c>
       <c r="F9">
-        <v>2.899911378937477</v>
+        <v>2.484788800676573</v>
       </c>
       <c r="G9">
-        <v>-11.96901370426017</v>
+        <v>-12.59468363736365</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-0.2525723127853166</v>
       </c>
       <c r="E10">
-        <v>-20.03513943293524</v>
+        <v>-18.23698655939152</v>
       </c>
       <c r="F10">
-        <v>2.410367292298243</v>
+        <v>2.200675126858568</v>
       </c>
       <c r="G10">
-        <v>-10.49871766663135</v>
+        <v>-12.58779439209643</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-0.01713309006474351</v>
       </c>
       <c r="E11">
-        <v>-19.17215266976751</v>
+        <v>-20.28807282015966</v>
       </c>
       <c r="F11">
-        <v>2.846120807519576</v>
+        <v>2.812074297749459</v>
       </c>
       <c r="G11">
-        <v>-10.81873486173054</v>
+        <v>-11.79649786566321</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>0.1269889988222258</v>
       </c>
       <c r="E12">
-        <v>-20.43204206581152</v>
+        <v>-20.1491754653964</v>
       </c>
       <c r="F12">
-        <v>2.932587983090739</v>
+        <v>2.818111384699114</v>
       </c>
       <c r="G12">
-        <v>-9.75709918656044</v>
+        <v>-10.31696871652536</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>0.1945654967284039</v>
       </c>
       <c r="E13">
-        <v>-20.27879397691795</v>
+        <v>-19.64397890510069</v>
       </c>
       <c r="F13">
-        <v>3.417759457697445</v>
+        <v>2.781017824747691</v>
       </c>
       <c r="G13">
-        <v>-9.600308439275016</v>
+        <v>-9.816112971343488</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>0.2024405665323288</v>
       </c>
       <c r="E14">
-        <v>-22.9409932765472</v>
+        <v>-20.64853935117022</v>
       </c>
       <c r="F14">
-        <v>3.163536649327443</v>
+        <v>2.962298306064383</v>
       </c>
       <c r="G14">
-        <v>-9.068757315853016</v>
+        <v>-10.79933506487041</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>0.1797280890340479</v>
       </c>
       <c r="E15">
-        <v>-22.56578203416766</v>
+        <v>-21.25442653102648</v>
       </c>
       <c r="F15">
-        <v>3.57375449036823</v>
+        <v>3.159971727311789</v>
       </c>
       <c r="G15">
-        <v>-8.705441495645701</v>
+        <v>-9.600967237837331</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>0.1514018340421248</v>
       </c>
       <c r="E16">
-        <v>-22.9999721220231</v>
+        <v>-24.38796299079608</v>
       </c>
       <c r="F16">
-        <v>3.865248233752184</v>
+        <v>3.399622857553832</v>
       </c>
       <c r="G16">
-        <v>-8.842782787887906</v>
+        <v>-8.164107710155156</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>0.1443531958381936</v>
       </c>
       <c r="E17">
-        <v>-24.02314006779014</v>
+        <v>-23.51183006758408</v>
       </c>
       <c r="F17">
-        <v>4.089295109609402</v>
+        <v>3.368347833135734</v>
       </c>
       <c r="G17">
-        <v>-8.406969330916089</v>
+        <v>-8.505269359613669</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>0.1754242673531916</v>
       </c>
       <c r="E18">
-        <v>-24.50849285498424</v>
+        <v>-24.02554015901421</v>
       </c>
       <c r="F18">
-        <v>4.001011423353231</v>
+        <v>4.407513890316397</v>
       </c>
       <c r="G18">
-        <v>-8.379604361488473</v>
+        <v>-7.862546806437403</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>0.2538328288797729</v>
       </c>
       <c r="E19">
-        <v>-26.04461916549614</v>
+        <v>-25.56897089810048</v>
       </c>
       <c r="F19">
-        <v>4.475991750394083</v>
+        <v>3.736290228469781</v>
       </c>
       <c r="G19">
-        <v>-7.53015148156688</v>
+        <v>-7.973287865271564</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>0.3746200286133478</v>
       </c>
       <c r="E20">
-        <v>-26.37350411877721</v>
+        <v>-26.91955657157011</v>
       </c>
       <c r="F20">
-        <v>4.491518403189052</v>
+        <v>3.795664946945521</v>
       </c>
       <c r="G20">
-        <v>-7.102915648087315</v>
+        <v>-7.125801449400297</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>0.5172721926906524</v>
       </c>
       <c r="E21">
-        <v>-26.8294580527135</v>
+        <v>-28.35789954283439</v>
       </c>
       <c r="F21">
-        <v>4.689948835864038</v>
+        <v>3.944197557342756</v>
       </c>
       <c r="G21">
-        <v>-7.532449000171134</v>
+        <v>-6.943641991647439</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>0.6505510365000579</v>
       </c>
       <c r="E22">
-        <v>-28.40877694831056</v>
+        <v>-27.92476458942274</v>
       </c>
       <c r="F22">
-        <v>4.885994207430371</v>
+        <v>4.118338692392647</v>
       </c>
       <c r="G22">
-        <v>-6.896569344624542</v>
+        <v>-6.623684386367957</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>0.734370392215469</v>
       </c>
       <c r="E23">
-        <v>-27.71495133169936</v>
+        <v>-28.24797083629819</v>
       </c>
       <c r="F23">
-        <v>4.770654489314832</v>
+        <v>4.176500292137161</v>
       </c>
       <c r="G23">
-        <v>-6.790870246646691</v>
+        <v>-7.286399324055881</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>0.7358274802354882</v>
       </c>
       <c r="E24">
-        <v>-28.41556513084806</v>
+        <v>-28.89705512971361</v>
       </c>
       <c r="F24">
-        <v>5.17794089070614</v>
+        <v>4.279582126467199</v>
       </c>
       <c r="G24">
-        <v>-6.935627160896863</v>
+        <v>-7.022975904950534</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>0.6267054872695522</v>
       </c>
       <c r="E25">
-        <v>-28.52050798750181</v>
+        <v>-28.2664560671975</v>
       </c>
       <c r="F25">
-        <v>4.848488883940934</v>
+        <v>4.018550966366723</v>
       </c>
       <c r="G25">
-        <v>-5.680841016783523</v>
+        <v>-6.521030990286237</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>0.3981896891102997</v>
       </c>
       <c r="E26">
-        <v>-28.97646192143811</v>
+        <v>-29.32556651116343</v>
       </c>
       <c r="F26">
-        <v>5.052546223733476</v>
+        <v>4.587731704963829</v>
       </c>
       <c r="G26">
-        <v>-6.232960559641015</v>
+        <v>-7.615308644473552</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>0.04878834268102501</v>
       </c>
       <c r="E27">
-        <v>-29.7588373187953</v>
+        <v>-29.2410651861803</v>
       </c>
       <c r="F27">
-        <v>4.935108095279979</v>
+        <v>3.885350212936857</v>
       </c>
       <c r="G27">
-        <v>-5.795389202987845</v>
+        <v>-6.81894698336525</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-0.4032542288386103</v>
       </c>
       <c r="E28">
-        <v>-28.92018657494479</v>
+        <v>-29.21171161766258</v>
       </c>
       <c r="F28">
-        <v>4.594327840101634</v>
+        <v>4.109245053026194</v>
       </c>
       <c r="G28">
-        <v>-5.524997085522332</v>
+        <v>-6.19655117980011</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-0.9348146071125711</v>
       </c>
       <c r="E29">
-        <v>-29.42410836980734</v>
+        <v>-28.47721577598848</v>
       </c>
       <c r="F29">
-        <v>4.70170626858026</v>
+        <v>4.144346310935993</v>
       </c>
       <c r="G29">
-        <v>-5.206443151551501</v>
+        <v>-6.868962705372559</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-1.508658386838441</v>
       </c>
       <c r="E30">
-        <v>-27.61146664367607</v>
+        <v>-27.73718613907702</v>
       </c>
       <c r="F30">
-        <v>4.508014284004269</v>
+        <v>4.258191010667358</v>
       </c>
       <c r="G30">
-        <v>-6.1281917249597</v>
+        <v>-5.981213434652677</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-2.088734314993156</v>
       </c>
       <c r="E31">
-        <v>-28.22986599721552</v>
+        <v>-29.30126671963827</v>
       </c>
       <c r="F31">
-        <v>4.451395213821393</v>
+        <v>3.883239132951576</v>
       </c>
       <c r="G31">
-        <v>-6.47749731644482</v>
+        <v>-5.554590052097877</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-2.634624033555842</v>
       </c>
       <c r="E32">
-        <v>-28.33930562855889</v>
+        <v>-28.03400949638378</v>
       </c>
       <c r="F32">
-        <v>4.726543528452097</v>
+        <v>3.90397301079651</v>
       </c>
       <c r="G32">
-        <v>-6.82589912899772</v>
+        <v>-5.26064009257491</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-3.115437173765566</v>
       </c>
       <c r="E33">
-        <v>-29.22749787805332</v>
+        <v>-26.94939468680665</v>
       </c>
       <c r="F33">
-        <v>4.62207911885788</v>
+        <v>3.884544106625898</v>
       </c>
       <c r="G33">
-        <v>-6.267221395426932</v>
+        <v>-6.181524613597358</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-3.506521976321924</v>
       </c>
       <c r="E34">
-        <v>-27.48503617785592</v>
+        <v>-26.38281013286297</v>
       </c>
       <c r="F34">
-        <v>4.756578511138406</v>
+        <v>3.383405708979732</v>
       </c>
       <c r="G34">
-        <v>-6.315118368289108</v>
+        <v>-5.908493991337045</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-3.797923894300895</v>
       </c>
       <c r="E35">
-        <v>-27.3025341468728</v>
+        <v>-27.13781090484379</v>
       </c>
       <c r="F35">
-        <v>4.651504374766745</v>
+        <v>3.780245986152803</v>
       </c>
       <c r="G35">
-        <v>-6.687296518905053</v>
+        <v>-7.558201733921124</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-3.989438822671066</v>
       </c>
       <c r="E36">
-        <v>-26.6328588821445</v>
+        <v>-25.60833239417515</v>
       </c>
       <c r="F36">
-        <v>4.197015618565763</v>
+        <v>3.625481492978313</v>
       </c>
       <c r="G36">
-        <v>-6.310135997252504</v>
+        <v>-6.480192100513787</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-4.091899529424336</v>
       </c>
       <c r="E37">
-        <v>-27.59684420110531</v>
+        <v>-26.89114492564599</v>
       </c>
       <c r="F37">
-        <v>4.357855207631878</v>
+        <v>4.159100115244227</v>
       </c>
       <c r="G37">
-        <v>-6.465605836867758</v>
+        <v>-7.629395015743151</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-4.121655706671766</v>
       </c>
       <c r="E38">
-        <v>-25.98689923579437</v>
+        <v>-26.19045867091316</v>
       </c>
       <c r="F38">
-        <v>4.485463895474327</v>
+        <v>4.112273098736513</v>
       </c>
       <c r="G38">
-        <v>-6.740066614801036</v>
+        <v>-8.013146833564388</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-4.099736320198271</v>
       </c>
       <c r="E39">
-        <v>-26.08981333609269</v>
+        <v>-25.55724667889462</v>
       </c>
       <c r="F39">
-        <v>4.406438553999814</v>
+        <v>4.126909708807005</v>
       </c>
       <c r="G39">
-        <v>-7.644534140494239</v>
+        <v>-6.150339274617424</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-4.048148174162582</v>
       </c>
       <c r="E40">
-        <v>-25.36273966331716</v>
+        <v>-24.29062344200121</v>
       </c>
       <c r="F40">
-        <v>4.450193181031575</v>
+        <v>4.101716115104194</v>
       </c>
       <c r="G40">
-        <v>-7.149137484906619</v>
+        <v>-7.462126391825935</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-3.988594282997243</v>
       </c>
       <c r="E41">
-        <v>-24.87785783741987</v>
+        <v>-22.62261891143793</v>
       </c>
       <c r="F41">
-        <v>4.433770150688468</v>
+        <v>4.19014075118684</v>
       </c>
       <c r="G41">
-        <v>-6.906491049605738</v>
+        <v>-7.728896772471486</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-3.939613083641279</v>
       </c>
       <c r="E42">
-        <v>-24.51995442269765</v>
+        <v>-23.19640373905381</v>
       </c>
       <c r="F42">
-        <v>4.531785709795015</v>
+        <v>4.421330140722691</v>
       </c>
       <c r="G42">
-        <v>-6.651860439452695</v>
+        <v>-7.882019435299396</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-3.916114481165336</v>
       </c>
       <c r="E43">
-        <v>-23.02047705232983</v>
+        <v>-22.99067063641134</v>
       </c>
       <c r="F43">
-        <v>4.540161930381775</v>
+        <v>4.697309900959</v>
       </c>
       <c r="G43">
-        <v>-6.493159507391113</v>
+        <v>-8.687518202096086</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-3.926632360726807</v>
       </c>
       <c r="E44">
-        <v>-22.62423104818466</v>
+        <v>-24.0733563160612</v>
       </c>
       <c r="F44">
-        <v>4.926123731621692</v>
+        <v>4.457679358893857</v>
       </c>
       <c r="G44">
-        <v>-7.4750971092488</v>
+        <v>-7.650585817740026</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-3.975550483567493</v>
       </c>
       <c r="E45">
-        <v>-21.20403367226912</v>
+        <v>-22.46696167437228</v>
       </c>
       <c r="F45">
-        <v>4.567236966712128</v>
+        <v>4.347706820125742</v>
       </c>
       <c r="G45">
-        <v>-7.617523399439325</v>
+        <v>-8.559982745741204</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-4.060461376457583</v>
       </c>
       <c r="E46">
-        <v>-21.63069743632381</v>
+        <v>-21.76695921921461</v>
       </c>
       <c r="F46">
-        <v>4.521892298941265</v>
+        <v>4.526836628809267</v>
       </c>
       <c r="G46">
-        <v>-7.865658719244318</v>
+        <v>-9.040528294039651</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-4.17702927465728</v>
       </c>
       <c r="E47">
-        <v>-21.79076087859892</v>
+        <v>-22.97858866775887</v>
       </c>
       <c r="F47">
-        <v>4.985058179852939</v>
+        <v>4.54524721007625</v>
       </c>
       <c r="G47">
-        <v>-8.154732245187938</v>
+        <v>-8.838422799412685</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-4.31706162469986</v>
       </c>
       <c r="E48">
-        <v>-21.34971468109588</v>
+        <v>-20.36758376678634</v>
       </c>
       <c r="F48">
-        <v>4.763721024817038</v>
+        <v>4.54212889312875</v>
       </c>
       <c r="G48">
-        <v>-7.86610564289212</v>
+        <v>-9.130333462883462</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-4.474050291259085</v>
       </c>
       <c r="E49">
-        <v>-20.98129614972785</v>
+        <v>-20.48651507964978</v>
       </c>
       <c r="F49">
-        <v>4.865822545185419</v>
+        <v>4.439789816873053</v>
       </c>
       <c r="G49">
-        <v>-8.156433865595124</v>
+        <v>-9.219105741519018</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-4.642754573077871</v>
       </c>
       <c r="E50">
-        <v>-20.16525607659764</v>
+        <v>-20.69128361732862</v>
       </c>
       <c r="F50">
-        <v>4.602642296157692</v>
+        <v>4.209655175476885</v>
       </c>
       <c r="G50">
-        <v>-8.114922935078203</v>
+        <v>-9.631046854607149</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-4.819996584376409</v>
       </c>
       <c r="E51">
-        <v>-20.83488152811185</v>
+        <v>-20.14790296420024</v>
       </c>
       <c r="F51">
-        <v>4.642502590343387</v>
+        <v>4.530903585600115</v>
       </c>
       <c r="G51">
-        <v>-7.983941200816938</v>
+        <v>-9.281575735845065</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-5.006809786373016</v>
       </c>
       <c r="E52">
-        <v>-18.40340797917341</v>
+        <v>-19.16462634596676</v>
       </c>
       <c r="F52">
-        <v>4.649386959957802</v>
+        <v>4.700928668975779</v>
       </c>
       <c r="G52">
-        <v>-8.085061814313976</v>
+        <v>-9.200103210123602</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-5.202953236868662</v>
       </c>
       <c r="E53">
-        <v>-18.60449939595802</v>
+        <v>-20.08067323908237</v>
       </c>
       <c r="F53">
-        <v>4.644428376736562</v>
+        <v>4.661217243146135</v>
       </c>
       <c r="G53">
-        <v>-8.546750495220737</v>
+        <v>-9.272809411257075</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-5.412347921082834</v>
       </c>
       <c r="E54">
-        <v>-18.62120946504632</v>
+        <v>-19.00340361434568</v>
       </c>
       <c r="F54">
-        <v>4.753027842475991</v>
+        <v>4.201817414901376</v>
       </c>
       <c r="G54">
-        <v>-9.31621397382246</v>
+        <v>-9.671538137097976</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-5.632651245374664</v>
       </c>
       <c r="E55">
-        <v>-18.766845189133</v>
+        <v>-17.5661203059992</v>
       </c>
       <c r="F55">
-        <v>4.644498059796841</v>
+        <v>4.797841968765181</v>
       </c>
       <c r="G55">
-        <v>-8.944231145393331</v>
+        <v>-8.987327827223563</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-5.865041869496025</v>
       </c>
       <c r="E56">
-        <v>-17.61486480021777</v>
+        <v>-17.88057301261782</v>
       </c>
       <c r="F56">
-        <v>4.554413699914814</v>
+        <v>4.684567403163374</v>
       </c>
       <c r="G56">
-        <v>-9.282416614412041</v>
+        <v>-9.637939410419913</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-6.101393539839951</v>
       </c>
       <c r="E57">
-        <v>-16.7492017089115</v>
+        <v>-17.00433140602964</v>
       </c>
       <c r="F57">
-        <v>4.79834558724629</v>
+        <v>4.286119664486133</v>
       </c>
       <c r="G57">
-        <v>-7.826829330614206</v>
+        <v>-9.840839435976305</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-6.337652253016181</v>
       </c>
       <c r="E58">
-        <v>-17.15808215553806</v>
+        <v>-17.56810830608857</v>
       </c>
       <c r="F58">
-        <v>4.702784772308674</v>
+        <v>4.507298448930491</v>
       </c>
       <c r="G58">
-        <v>-8.230560290764945</v>
+        <v>-9.930244028809861</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-6.561519341035436</v>
       </c>
       <c r="E59">
-        <v>-16.70959567524041</v>
+        <v>-15.88117928264724</v>
       </c>
       <c r="F59">
-        <v>4.711178413660503</v>
+        <v>4.31958970530303</v>
       </c>
       <c r="G59">
-        <v>-9.506914639066638</v>
+        <v>-10.40257942417092</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-6.766371974980502</v>
       </c>
       <c r="E60">
-        <v>-15.8322128932023</v>
+        <v>-16.29264548793218</v>
       </c>
       <c r="F60">
-        <v>4.540217360088815</v>
+        <v>4.394662116812606</v>
       </c>
       <c r="G60">
-        <v>-9.266999403835655</v>
+        <v>-9.961892844165295</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-6.939085230249815</v>
       </c>
       <c r="E61">
-        <v>-15.71286948920415</v>
+        <v>-14.82104087508157</v>
       </c>
       <c r="F61">
-        <v>4.37618977101492</v>
+        <v>4.631383391111086</v>
       </c>
       <c r="G61">
-        <v>-9.676841631051888</v>
+        <v>-10.00009653968848</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-7.076690977061008</v>
       </c>
       <c r="E62">
-        <v>-14.85836002937878</v>
+        <v>-15.63592618733983</v>
       </c>
       <c r="F62">
-        <v>4.309181590026762</v>
+        <v>4.467517340040567</v>
       </c>
       <c r="G62">
-        <v>-9.429282346170728</v>
+        <v>-10.15357674143464</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-7.170913400553342</v>
       </c>
       <c r="E63">
-        <v>-15.07916842199279</v>
+        <v>-14.8127356537515</v>
       </c>
       <c r="F63">
-        <v>4.492221568615507</v>
+        <v>4.318232469333498</v>
       </c>
       <c r="G63">
-        <v>-9.248738434641034</v>
+        <v>-10.02865661605578</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-7.223337053576074</v>
       </c>
       <c r="E64">
-        <v>-15.33327468398519</v>
+        <v>-14.38387105132909</v>
       </c>
       <c r="F64">
-        <v>4.582063621492471</v>
+        <v>4.859359441344511</v>
       </c>
       <c r="G64">
-        <v>-9.517409068426128</v>
+        <v>-10.84693739917959</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-7.232420023077173</v>
       </c>
       <c r="E65">
-        <v>-14.54117212445953</v>
+        <v>-15.32319430084412</v>
       </c>
       <c r="F65">
-        <v>4.668584643064759</v>
+        <v>3.777560020920217</v>
       </c>
       <c r="G65">
-        <v>-9.725261670109269</v>
+        <v>-10.86641333858713</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-7.201061707113789</v>
       </c>
       <c r="E66">
-        <v>-15.18522075477842</v>
+        <v>-14.6349115364183</v>
       </c>
       <c r="F66">
-        <v>4.39478564587401</v>
+        <v>3.946948454517874</v>
       </c>
       <c r="G66">
-        <v>-9.496248061339106</v>
+        <v>-10.43899211455736</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-7.129617957006769</v>
       </c>
       <c r="E67">
-        <v>-14.2857571334789</v>
+        <v>-14.72947060217247</v>
       </c>
       <c r="F67">
-        <v>4.276067883040839</v>
+        <v>3.981362384060374</v>
       </c>
       <c r="G67">
-        <v>-9.551299123111646</v>
+        <v>-10.46954182879376</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-7.022374482840598</v>
       </c>
       <c r="E68">
-        <v>-14.30833610488115</v>
+        <v>-13.61864951351295</v>
       </c>
       <c r="F68">
-        <v>4.060644285893187</v>
+        <v>3.580592932511098</v>
       </c>
       <c r="G68">
-        <v>-9.604165224828268</v>
+        <v>-10.04972823841324</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-6.881059976861482</v>
       </c>
       <c r="E69">
-        <v>-14.43528281673817</v>
+        <v>-14.09553858278671</v>
       </c>
       <c r="F69">
-        <v>3.985872778507545</v>
+        <v>3.683628839369588</v>
       </c>
       <c r="G69">
-        <v>-9.503372355339618</v>
+        <v>-10.63810818656237</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-6.710972843774053</v>
       </c>
       <c r="E70">
-        <v>-14.47104417597674</v>
+        <v>-13.71843896674598</v>
       </c>
       <c r="F70">
-        <v>3.739145650235318</v>
+        <v>3.885945686361062</v>
       </c>
       <c r="G70">
-        <v>-10.84535164786628</v>
+        <v>-9.291149833544639</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-6.513660795145054</v>
       </c>
       <c r="E71">
-        <v>-14.82597691174993</v>
+        <v>-16.11130727476903</v>
       </c>
       <c r="F71">
-        <v>4.033100472611864</v>
+        <v>4.068307838817999</v>
       </c>
       <c r="G71">
-        <v>-9.305984388106111</v>
+        <v>-10.34039413676125</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-6.294538644273457</v>
       </c>
       <c r="E72">
-        <v>-13.49797473815655</v>
+        <v>-14.22560088476101</v>
       </c>
       <c r="F72">
-        <v>3.847729278915593</v>
+        <v>3.984125950882815</v>
       </c>
       <c r="G72">
-        <v>-9.443809019997049</v>
+        <v>-10.24758630311332</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-6.055847693790295</v>
       </c>
       <c r="E73">
-        <v>-14.36909916911607</v>
+        <v>-14.59339448671598</v>
       </c>
       <c r="F73">
-        <v>3.66057008124079</v>
+        <v>3.279706229342673</v>
       </c>
       <c r="G73">
-        <v>-9.404436701898497</v>
+        <v>-9.627878662526067</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-5.805087391549296</v>
       </c>
       <c r="E74">
-        <v>-14.74335490347998</v>
+        <v>-15.14004922655191</v>
       </c>
       <c r="F74">
-        <v>3.634020835274363</v>
+        <v>3.098183441020919</v>
       </c>
       <c r="G74">
-        <v>-9.62741518615057</v>
+        <v>-10.15405345999229</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-5.544153980812352</v>
       </c>
       <c r="E75">
-        <v>-15.32402754006153</v>
+        <v>-15.18551510558892</v>
       </c>
       <c r="F75">
-        <v>3.621653675780697</v>
+        <v>3.487686408687758</v>
       </c>
       <c r="G75">
-        <v>-9.976479107811324</v>
+        <v>-9.593660863832159</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-5.280258777345611</v>
       </c>
       <c r="E76">
-        <v>-14.69013627694184</v>
+        <v>-14.25625412531893</v>
       </c>
       <c r="F76">
-        <v>3.835550580425863</v>
+        <v>3.750353536998883</v>
       </c>
       <c r="G76">
-        <v>-9.449046303040177</v>
+        <v>-10.40161274487345</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-5.013424494010042</v>
       </c>
       <c r="E77">
-        <v>-15.63960783670806</v>
+        <v>-14.75888756932629</v>
       </c>
       <c r="F77">
-        <v>3.356013931466292</v>
+        <v>2.734903475901926</v>
       </c>
       <c r="G77">
-        <v>-8.889934888003745</v>
+        <v>-8.485627892929173</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-4.751159137515864</v>
       </c>
       <c r="E78">
-        <v>-15.9045371515788</v>
+        <v>-16.21285377591703</v>
       </c>
       <c r="F78">
-        <v>3.443984043951207</v>
+        <v>2.816166593834954</v>
       </c>
       <c r="G78">
-        <v>-8.817463735603559</v>
+        <v>-9.134127348071466</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-4.492727045397482</v>
       </c>
       <c r="E79">
-        <v>-15.74994863437896</v>
+        <v>-16.09951965692706</v>
       </c>
       <c r="F79">
-        <v>3.083817644661968</v>
+        <v>3.131688323367956</v>
       </c>
       <c r="G79">
-        <v>-8.518882322871152</v>
+        <v>-8.458872063880783</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-4.246833084584765</v>
       </c>
       <c r="E80">
-        <v>-17.75100884278437</v>
+        <v>-15.83420542176567</v>
       </c>
       <c r="F80">
-        <v>3.337107650247775</v>
+        <v>2.522091409808835</v>
       </c>
       <c r="G80">
-        <v>-8.335855502187005</v>
+        <v>-8.662980438559009</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-4.014595102625564</v>
       </c>
       <c r="E81">
-        <v>-18.03387091472548</v>
+        <v>-15.84455751334721</v>
       </c>
       <c r="F81">
-        <v>3.453036506963858</v>
+        <v>3.03231077717413</v>
       </c>
       <c r="G81">
-        <v>-8.426660455783674</v>
+        <v>-9.230914457457599</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-3.806327447932974</v>
       </c>
       <c r="E82">
-        <v>-17.17624586478283</v>
+        <v>-17.13699758055835</v>
       </c>
       <c r="F82">
-        <v>2.82438444383017</v>
+        <v>2.710929335754003</v>
       </c>
       <c r="G82">
-        <v>-8.111327682622555</v>
+        <v>-8.360062211170156</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-3.626657641294567</v>
       </c>
       <c r="E83">
-        <v>-18.59154796029608</v>
+        <v>-16.54902504387644</v>
       </c>
       <c r="F83">
-        <v>3.347802416294738</v>
+        <v>3.063908877598978</v>
       </c>
       <c r="G83">
-        <v>-8.225117753898383</v>
+        <v>-9.398878295938061</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-3.48681649436173</v>
       </c>
       <c r="E84">
-        <v>-20.06158572114004</v>
+        <v>-17.42198803528307</v>
       </c>
       <c r="F84">
-        <v>3.067730359972933</v>
+        <v>2.902313860811199</v>
       </c>
       <c r="G84">
-        <v>-8.130571883842338</v>
+        <v>-8.74496278829352</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-3.395387726981025</v>
       </c>
       <c r="E85">
-        <v>-19.73926252669608</v>
+        <v>-20.36232167998942</v>
       </c>
       <c r="F85">
-        <v>3.111996524015381</v>
+        <v>2.862987275519006</v>
       </c>
       <c r="G85">
-        <v>-7.398934698572327</v>
+        <v>-9.058160259581809</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-3.362813057932521</v>
       </c>
       <c r="E86">
-        <v>-22.23077911250223</v>
+        <v>-20.87502192171584</v>
       </c>
       <c r="F86">
-        <v>3.123025452010502</v>
+        <v>2.629260789106622</v>
       </c>
       <c r="G86">
-        <v>-7.365637231538337</v>
+        <v>-7.873594096901951</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-3.398646548263247</v>
       </c>
       <c r="E87">
-        <v>-22.8002483043888</v>
+        <v>-21.16923687799418</v>
       </c>
       <c r="F87">
-        <v>2.574793975262828</v>
+        <v>2.633516206901408</v>
       </c>
       <c r="G87">
-        <v>-7.238058738091444</v>
+        <v>-6.450701760849959</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-3.50862271993651</v>
       </c>
       <c r="E88">
-        <v>-23.75420305342261</v>
+        <v>-21.40072794079228</v>
       </c>
       <c r="F88">
-        <v>2.783695871450699</v>
+        <v>2.556630452118653</v>
       </c>
       <c r="G88">
-        <v>-6.84357082108635</v>
+        <v>-6.907712640909729</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-3.701095704481965</v>
       </c>
       <c r="E89">
-        <v>-25.07802544550691</v>
+        <v>-24.06589791937057</v>
       </c>
       <c r="F89">
-        <v>2.595135094040733</v>
+        <v>2.799821165081704</v>
       </c>
       <c r="G89">
-        <v>-6.766070950012011</v>
+        <v>-5.755467334329774</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-3.975253908538892</v>
       </c>
       <c r="E90">
-        <v>-26.74476653182205</v>
+        <v>-26.11654944663397</v>
       </c>
       <c r="F90">
-        <v>2.689981657610486</v>
+        <v>2.390512371236379</v>
       </c>
       <c r="G90">
-        <v>-6.306928078624951</v>
+        <v>-5.890547523968657</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-4.336736361571843</v>
       </c>
       <c r="E91">
-        <v>-28.07568504267637</v>
+        <v>-26.68114147201428</v>
       </c>
       <c r="F91">
-        <v>2.355214733793064</v>
+        <v>1.759519590759671</v>
       </c>
       <c r="G91">
-        <v>-5.80881677569513</v>
+        <v>-5.31037772875692</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-4.776647992322061</v>
       </c>
       <c r="E92">
-        <v>-30.13652790069404</v>
+        <v>-29.30713562195221</v>
       </c>
       <c r="F92">
-        <v>2.526304067543903</v>
+        <v>1.858958901484198</v>
       </c>
       <c r="G92">
-        <v>-5.933591237070261</v>
+        <v>-6.531667773103915</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-5.295550279335132</v>
       </c>
       <c r="E93">
-        <v>-31.68568489516301</v>
+        <v>-30.32399993190058</v>
       </c>
       <c r="F93">
-        <v>2.345761593183807</v>
+        <v>1.878758392839022</v>
       </c>
       <c r="G93">
-        <v>-6.223330182667275</v>
+        <v>-6.319163854938097</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-5.874544467140153</v>
       </c>
       <c r="E94">
-        <v>-33.8358111467159</v>
+        <v>-33.20207385171248</v>
       </c>
       <c r="F94">
-        <v>1.617546690264186</v>
+        <v>1.619396458773419</v>
       </c>
       <c r="G94">
-        <v>-5.222092100315637</v>
+        <v>-5.451648638554239</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-6.504608466832289</v>
       </c>
       <c r="E95">
-        <v>-35.44799091394962</v>
+        <v>-34.0237881027743</v>
       </c>
       <c r="F95">
-        <v>1.81312645229138</v>
+        <v>1.738879151563748</v>
       </c>
       <c r="G95">
-        <v>-5.480380863289574</v>
+        <v>-6.405747862972196</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-7.163570023500548</v>
       </c>
       <c r="E96">
-        <v>-36.95830718685481</v>
+        <v>-35.68095373080022</v>
       </c>
       <c r="F96">
-        <v>1.60602998084711</v>
+        <v>1.153180360268608</v>
       </c>
       <c r="G96">
-        <v>-5.532386223165985</v>
+        <v>-6.31415499953718</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-7.833064759916244</v>
       </c>
       <c r="E97">
-        <v>-39.31196570268245</v>
+        <v>-39.53121856447482</v>
       </c>
       <c r="F97">
-        <v>1.22277790042851</v>
+        <v>0.7708990915761728</v>
       </c>
       <c r="G97">
-        <v>-6.248675719315935</v>
+        <v>-4.897128950180776</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-8.501317313256983</v>
       </c>
       <c r="E98">
-        <v>-42.47140729801293</v>
+        <v>-39.41541416291367</v>
       </c>
       <c r="F98">
-        <v>1.361003752728065</v>
+        <v>1.057112759438051</v>
       </c>
       <c r="G98">
-        <v>-6.204913617832309</v>
+        <v>-5.636092372729195</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-9.144332838607346</v>
       </c>
       <c r="E99">
-        <v>-44.29902468768756</v>
+        <v>-42.70352555446109</v>
       </c>
       <c r="F99">
-        <v>0.7647606474479295</v>
+        <v>0.5135761788766982</v>
       </c>
       <c r="G99">
-        <v>-5.787678942426883</v>
+        <v>-5.450483326524417</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-9.778350429022852</v>
       </c>
       <c r="E100">
-        <v>-46.23977015078481</v>
+        <v>-44.40052363985848</v>
       </c>
       <c r="F100">
-        <v>0.679012474362376</v>
+        <v>0.2184652511818806</v>
       </c>
       <c r="G100">
-        <v>-5.892457708744816</v>
+        <v>-6.206337152414195</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-10.36334934108399</v>
       </c>
       <c r="E101">
-        <v>-48.51490153096394</v>
+        <v>-46.14397934010056</v>
       </c>
       <c r="F101">
-        <v>0.5924756157309337</v>
+        <v>0.1790626480057472</v>
       </c>
       <c r="G101">
-        <v>-5.594816490945561</v>
+        <v>-5.496288034605772</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-10.97570752044046</v>
       </c>
       <c r="E102">
-        <v>-50.29769382067364</v>
+        <v>-50.1589266595381</v>
       </c>
       <c r="F102">
-        <v>0.176065484560778</v>
+        <v>-0.5373172206077942</v>
       </c>
       <c r="G102">
-        <v>-6.458597411961121</v>
+        <v>-6.404983126952624</v>
       </c>
     </row>
   </sheetData>
